--- a/samples/예시데이터_구매현황(26.08).xlsx
+++ b/samples/예시데이터_구매현황(26.08).xlsx
@@ -555,7 +555,7 @@
         <v>22000</v>
       </c>
       <c r="M3">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="N3" t="str">
         <v>EA</v>
@@ -564,7 +564,7 @@
         <v/>
       </c>
       <c r="P3">
-        <v>2200000</v>
+        <v>2420000</v>
       </c>
       <c r="Q3" t="str">
         <v>본사</v>
@@ -614,7 +614,7 @@
         <v>14000</v>
       </c>
       <c r="M4">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N4" t="str">
         <v>EA</v>
@@ -623,7 +623,7 @@
         <v/>
       </c>
       <c r="P4">
-        <v>1400000</v>
+        <v>560000</v>
       </c>
       <c r="Q4" t="str">
         <v>본사</v>
@@ -673,7 +673,7 @@
         <v>5000</v>
       </c>
       <c r="M5">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N5" t="str">
         <v>EA</v>
@@ -682,7 +682,7 @@
         <v/>
       </c>
       <c r="P5">
-        <v>500000</v>
+        <v>600000</v>
       </c>
       <c r="Q5" t="str">
         <v>본사</v>
@@ -732,7 +732,7 @@
         <v>60000</v>
       </c>
       <c r="M6">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="N6" t="str">
         <v>EA</v>
@@ -741,7 +741,7 @@
         <v/>
       </c>
       <c r="P6">
-        <v>6000000</v>
+        <v>2700000</v>
       </c>
       <c r="Q6" t="str">
         <v>본사</v>
@@ -791,7 +791,7 @@
         <v>2000</v>
       </c>
       <c r="M7">
-        <v>100</v>
+        <v>410</v>
       </c>
       <c r="N7" t="str">
         <v>EA</v>
@@ -800,7 +800,7 @@
         <v/>
       </c>
       <c r="P7">
-        <v>200000</v>
+        <v>820000</v>
       </c>
       <c r="Q7" t="str">
         <v>본사</v>
@@ -909,7 +909,7 @@
         <v>9000</v>
       </c>
       <c r="M9">
-        <v>100</v>
+        <v>180</v>
       </c>
       <c r="N9" t="str">
         <v>EA</v>
@@ -918,7 +918,7 @@
         <v/>
       </c>
       <c r="P9">
-        <v>900000</v>
+        <v>1620000</v>
       </c>
       <c r="Q9" t="str">
         <v>대구</v>
@@ -968,7 +968,7 @@
         <v>5000</v>
       </c>
       <c r="M10">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="N10" t="str">
         <v>EA</v>
@@ -977,7 +977,7 @@
         <v/>
       </c>
       <c r="P10">
-        <v>500000</v>
+        <v>225000</v>
       </c>
       <c r="Q10" t="str">
         <v>예시수출(가상)</v>
@@ -1027,7 +1027,7 @@
         <v>12000</v>
       </c>
       <c r="M11">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="N11" t="str">
         <v>EA</v>
@@ -1036,7 +1036,7 @@
         <v/>
       </c>
       <c r="P11">
-        <v>1200000</v>
+        <v>480000</v>
       </c>
       <c r="Q11" t="str">
         <v>본사</v>
@@ -1086,7 +1086,7 @@
         <v>12000</v>
       </c>
       <c r="M12">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="N12" t="str">
         <v>EA</v>
@@ -1095,7 +1095,7 @@
         <v/>
       </c>
       <c r="P12">
-        <v>1200000</v>
+        <v>1440000</v>
       </c>
       <c r="Q12" t="str">
         <v>본사</v>
@@ -1145,7 +1145,7 @@
         <v>9000</v>
       </c>
       <c r="M13">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="N13" t="str">
         <v>EA</v>
@@ -1154,7 +1154,7 @@
         <v/>
       </c>
       <c r="P13">
-        <v>900000</v>
+        <v>990000</v>
       </c>
       <c r="Q13" t="str">
         <v>본사</v>
@@ -1204,7 +1204,7 @@
         <v>50000</v>
       </c>
       <c r="M14">
-        <v>100</v>
+        <v>12</v>
       </c>
       <c r="N14" t="str">
         <v>EA</v>
@@ -1213,7 +1213,7 @@
         <v/>
       </c>
       <c r="P14">
-        <v>5000000</v>
+        <v>600000</v>
       </c>
       <c r="Q14" t="str">
         <v>본사</v>
@@ -1263,7 +1263,7 @@
         <v>1800</v>
       </c>
       <c r="M15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="N15" t="str">
         <v>EA</v>
@@ -1272,7 +1272,7 @@
         <v/>
       </c>
       <c r="P15">
-        <v>180000</v>
+        <v>270000</v>
       </c>
       <c r="Q15" t="str">
         <v>본사</v>
@@ -1322,7 +1322,7 @@
         <v>20000</v>
       </c>
       <c r="M16">
-        <v>100</v>
+        <v>45</v>
       </c>
       <c r="N16" t="str">
         <v>EA</v>
@@ -1331,7 +1331,7 @@
         <v/>
       </c>
       <c r="P16">
-        <v>2000000</v>
+        <v>900000</v>
       </c>
       <c r="Q16" t="str">
         <v>본사</v>
@@ -1449,7 +1449,7 @@
         <v/>
       </c>
       <c r="P18">
-        <v>27180000</v>
+        <v>18625000</v>
       </c>
       <c r="Q18" t="str">
         <v/>
@@ -1508,7 +1508,7 @@
         <v/>
       </c>
       <c r="P19">
-        <v>27180000</v>
+        <v>18625000</v>
       </c>
       <c r="Q19" t="str">
         <v/>
